--- a/dataset_t6_grouped/results2/G3/G3_T2677_W0056F0003T0006Z000C1N57_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T2677_W0056F0003T0006Z000C1N57_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>22.05924395878181</v>
+        <v>3.584627143302044</v>
       </c>
       <c r="D2" t="n">
-        <v>22.09167500523601</v>
+        <v>3.589897188350851</v>
       </c>
       <c r="E2" t="n">
-        <v>6.447280602382513</v>
+        <v>1.047683097887159</v>
       </c>
       <c r="F2" t="n">
-        <v>6.339388473346095</v>
+        <v>1.03015062691874</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>6.351705534478676</v>
+        <v>1.032152149352785</v>
       </c>
       <c r="D3" t="n">
-        <v>6.668108818373865</v>
+        <v>1.083567682985753</v>
       </c>
       <c r="E3" t="n">
-        <v>6.447280602382513</v>
+        <v>1.047683097887159</v>
       </c>
       <c r="F3" t="n">
-        <v>6.339388473346095</v>
+        <v>1.03015062691874</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>12.7883121825111</v>
+        <v>2.078100729658054</v>
       </c>
       <c r="D4" t="n">
-        <v>12.8208817990789</v>
+        <v>2.083393292350321</v>
       </c>
       <c r="E4" t="n">
-        <v>6.447280602382513</v>
+        <v>1.047683097887159</v>
       </c>
       <c r="F4" t="n">
-        <v>6.339388473346095</v>
+        <v>1.03015062691874</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
